--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.32-33-information-protection/WKBK/90_workbooks/ISMS-IMP-A.5.32-33.S3_Retention_Disposal_Schedule_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.32-33-information-protection/WKBK/90_workbooks/ISMS-IMP-A.5.32-33.S3_Retention_Disposal_Schedule_20260208.xlsx
@@ -603,14 +603,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- Restricted: Cross-cut shredding P-5, NIST 800-88 Purge, witnessed destruction</t>
+          <t>- Restricted: Cross-cut shredding P-5, NIST 800-88 Rev. 2 Purge, witnessed destruction</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- Confidential: Cross-cut shredding P-4, NIST 800-88 Clear</t>
+          <t>- Confidential: Cross-cut shredding P-4, NIST 800-88 Rev. 2 Clear</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>NIST 800-88 Purge, cryptographic erasure</t>
+          <t>NIST 800-88 Rev. 2 Purge, cryptographic erasure</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>NIST 800-88 Clear, secure deletion</t>
+          <t>NIST 800-88 Rev. 2 Clear, secure deletion</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
